--- a/Result/profitability/8046.xlsx
+++ b/Result/profitability/8046.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0.95</v>
+        <v>1.37625</v>
       </c>
       <c r="N2" t="n">
-        <v>10.165</v>
+        <v>12.5275</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.68</v>
       </c>
       <c r="M3" t="n">
-        <v>1.27375</v>
+        <v>1.67625</v>
       </c>
       <c r="N3" t="n">
-        <v>12.115</v>
+        <v>15.18125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>4.07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7475</v>
+        <v>2.145</v>
       </c>
       <c r="N4" t="n">
-        <v>15.14125</v>
+        <v>17.59875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,13 +914,13 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>1.92</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9475</v>
+        <v>2.42125</v>
       </c>
       <c r="N5" t="n">
-        <v>17.21125</v>
+        <v>19.3025</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>-0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9275</v>
+        <v>2.225</v>
       </c>
       <c r="N6" t="n">
-        <v>15.37875</v>
+        <v>17.27625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>1.07</v>
       </c>
       <c r="M7" t="n">
-        <v>1.92125</v>
+        <v>2.12625</v>
       </c>
       <c r="N7" t="n">
-        <v>16.01</v>
+        <v>17.53875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.38</v>
       </c>
       <c r="M8" t="n">
-        <v>1.86125</v>
+        <v>2.045</v>
       </c>
       <c r="N8" t="n">
-        <v>16.645</v>
+        <v>17.7575</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13575</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10216</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3360</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2899</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>76</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2976</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2262</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.11375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.23375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7241379310344829</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5615141955835963</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-13.06896551724138</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.086034912718205</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
